--- a/list/card_option.xlsx
+++ b/list/card_option.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\checc\PycharmProjects\redprinting_crolling2\list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550FA9A5-5D66-4623-80B5-EDD2BF807301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8D6FB4-289B-448C-8E5F-C4EA4DB2626D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-120" windowWidth="17310" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="131">
   <si>
     <t>BCSPDFT</t>
   </si>
@@ -495,23 +495,27 @@
     <t>TPTKDFT</t>
   </si>
   <si>
-    <t>PRCAFIL</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>스노우_300</t>
-  </si>
-  <si>
-    <t>양면,단면</t>
-  </si>
-  <si>
-    <t>55X85(59X89),54X86(58X90)</t>
-  </si>
-  <si>
-    <t>양면 무광,양면 유광</t>
-  </si>
-  <si>
-    <t>1,10,20,30,40,50,100,200,300,400,500,1000,2000,3000,4000,5000,10000,20000</t>
+    <t>x</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>단면,양면</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>150X300(154x304),150X105(154x109),150X100(154x104),150X200(154x204)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>반누보화이트,아코팩,띤또레또,매쉬멜로우White,랑데뷰울트라화이트,랑데뷰내츄럴,스코틀랜드</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRKCHIG</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,200,300,400,500,1000</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1520,7 +1524,7 @@
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.25" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5" style="1" bestFit="1" customWidth="1"/>
@@ -1577,22 +1581,34 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>129</v>
+      <c r="G3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:10">
